--- a/unilabos/devices/eit_synthesis_station/sheet/reaction_template.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/reaction_template.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>679</v>
+        <v>710</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>

--- a/unilabos/devices/eit_synthesis_station/sheet/reaction_template.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/reaction_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -466,15 +466,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" style="6" min="1" max="1"/>
-    <col width="37.81640625" customWidth="1" style="6" min="2" max="2"/>
+    <col width="51.90625" customWidth="1" style="6" min="2" max="2"/>
     <col width="15.6328125" customWidth="1" style="4" min="3" max="4"/>
-    <col width="13" customWidth="1" style="4" min="5" max="5"/>
-    <col width="28.453125" customWidth="1" style="4" min="6" max="6"/>
-    <col width="13" customWidth="1" style="4" min="7" max="7"/>
-    <col width="20.81640625" customWidth="1" style="4" min="8" max="8"/>
-    <col width="19.08984375" customWidth="1" style="4" min="9" max="9"/>
-    <col width="17.81640625" customWidth="1" style="4" min="10" max="10"/>
-    <col width="15.6328125" customWidth="1" style="4" min="11" max="14"/>
+    <col width="13.90625" customWidth="1" style="4" min="5" max="5"/>
+    <col width="14.6328125" customWidth="1" style="4" min="6" max="6"/>
+    <col width="14.453125" customWidth="1" style="4" min="7" max="7"/>
+    <col width="34.81640625" customWidth="1" style="4" min="8" max="8"/>
+    <col width="14.453125" customWidth="1" style="4" min="9" max="9"/>
+    <col width="14.453125" customWidth="1" min="10" max="10"/>
+    <col width="14.1796875" customWidth="1" min="11" max="11"/>
+    <col width="15.6328125" customWidth="1" style="4" min="12" max="13"/>
+    <col width="21.90625" customWidth="1" style="4" min="14" max="14"/>
     <col width="16.6328125" customWidth="1" style="4" min="15" max="15"/>
     <col width="15.6328125" customWidth="1" style="4" min="16" max="16"/>
     <col width="17.81640625" customWidth="1" style="4" min="17" max="17"/>
@@ -565,7 +567,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Cu催化不对称C-N偶联测试_20260225_140143</t>
+          <t xml:space="preserve">Cu_Catalyst_Ullmann coupling </t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -583,9 +585,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -593,22 +595,12 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>NNP-77</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>碘化亚铜</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -620,7 +612,7 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -643,7 +635,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -660,9 +652,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -670,22 +662,22 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>NNP-1</t>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
+          <t>0.1eq</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>碘化亚铜</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -697,7 +689,7 @@
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -735,9 +727,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -745,22 +737,22 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>磺酰胺奎宁</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+          <t>0.2eq</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>碘化亚铜</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -772,7 +764,7 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -796,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -813,9 +805,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -823,12 +815,12 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>碘化亚铜</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -840,12 +832,12 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>四氢呋喃</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -882,9 +874,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -892,26 +884,26 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>NNP-77</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>噻吩-2-甲酸铜(I)</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
           <t>0.1eq</t>
         </is>
       </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>0.1eq</t>
+        </is>
+      </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
           <t>碳酸铯</t>
@@ -919,12 +911,12 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>四氢呋喃</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -942,7 +934,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -959,9 +951,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -969,22 +961,22 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>NNP-1</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>噻吩-2-甲酸铜(I)</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
+          <t>0.2eq</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -996,12 +988,12 @@
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>四氢呋喃</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1019,7 +1011,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1036,9 +1028,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1046,22 +1038,12 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>磺酰胺奎宁</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>噻吩-2-甲酸铜(I)</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -1073,12 +1055,12 @@
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>N,N-二甲基甲酰胺</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1114,9 +1096,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1124,16 +1106,26 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>噻吩-2-甲酸铜(I)</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
       </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>0.1eq</t>
+        </is>
+      </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
           <t>碳酸铯</t>
@@ -1141,12 +1133,12 @@
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>N,N-二甲基甲酰胺</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1182,9 +1174,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1192,22 +1184,22 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>NNP-77</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>六氟磷酸四乙氰铜</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
+          <t>0.2eq</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -1219,12 +1211,12 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>N,N-二甲基甲酰胺</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1262,9 +1254,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1272,22 +1264,12 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>NNP-1</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>六氟磷酸四乙氰铜</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -1299,12 +1281,12 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>乙腈</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1337,9 +1319,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1347,26 +1329,26 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>磺酰胺奎宁</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>0.15eq</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>六氟磷酸四乙氰铜</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
           <t>0.1eq</t>
         </is>
       </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>0.1eq</t>
+        </is>
+      </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
           <t>碳酸铯</t>
@@ -1374,12 +1356,12 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>乙腈</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1415,9 +1397,9 @@
           <t>1.0eq</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>2-氯-N-苯基-丙酰胺</t>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>碘苯</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1425,12 +1407,22 @@
           <t>1.5eq</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>六氟磷酸四乙氰铜</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2,2,6,6-四甲基-3,5-庚二酮</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>0.2eq</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>碘化亚铜</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>0.1eq</t>
         </is>
@@ -1442,12 +1434,12 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>3.0eq</t>
+          <t>2.0eq</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>1,4-二氧六环</t>
+          <t>乙腈</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1475,8 +1467,6 @@
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
@@ -1498,8 +1488,6 @@
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
@@ -1526,8 +1514,6 @@
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
@@ -1554,8 +1540,6 @@
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n"/>
@@ -1577,8 +1561,6 @@
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n"/>
@@ -1601,8 +1583,6 @@
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
@@ -1627,8 +1607,6 @@
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n"/>
@@ -1650,8 +1628,6 @@
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
@@ -1678,8 +1654,6 @@
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
@@ -1695,7 +1669,7 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
@@ -1704,8 +1678,6 @@
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
@@ -1730,8 +1702,6 @@
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n"/>
@@ -1753,8 +1723,6 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
@@ -1781,8 +1749,6 @@
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="3" t="n"/>
@@ -1803,8 +1769,6 @@
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="3" t="n"/>
@@ -1825,8 +1789,6 @@
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="3" t="n"/>
@@ -1844,8 +1806,6 @@
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="3" t="n"/>
@@ -1868,8 +1828,6 @@
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="3" t="n"/>
@@ -1888,8 +1846,6 @@
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="3" t="n"/>

--- a/unilabos/devices/eit_synthesis_station/sheet/reaction_template.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/reaction_template.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>五联烯合成-3</t>
+          <t>五联烯合成-3_20260304_133950</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
